--- a/master-exports/master_kategori_menu.xlsx
+++ b/master-exports/master_kategori_menu.xlsx
@@ -7,15 +7,15 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Kategori Menu" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
     <t>name</t>
   </si>
@@ -23,7 +23,40 @@
     <t>sort_order</t>
   </si>
   <si>
-    <t>Ice Cream</t>
+    <t>Ice Cone</t>
+  </si>
+  <si>
+    <t>Sundae</t>
+  </si>
+  <si>
+    <t>Creamy Series</t>
+  </si>
+  <si>
+    <t>Fruit Tea</t>
+  </si>
+  <si>
+    <t>Fresh Tea</t>
+  </si>
+  <si>
+    <t>Milk Tea</t>
+  </si>
+  <si>
+    <t>Milky Fruity</t>
+  </si>
+  <si>
+    <t>Ice Cream Coffee</t>
+  </si>
+  <si>
+    <t>Latte Series</t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>Merchandise</t>
+  </si>
+  <si>
+    <t>Additional Topping</t>
   </si>
 </sst>
 </file>
@@ -47,16 +80,22 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1e40af"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -73,7 +112,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -373,8 +414,12 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15.139" bestFit="true" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
@@ -390,6 +435,94 @@
       </c>
       <c r="B2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
